--- a/AnfibiosEcuador a 26 Noviembre 2025. Actualizado de Coloma Duellman 2025.xlsx
+++ b/AnfibiosEcuador a 26 Noviembre 2025. Actualizado de Coloma Duellman 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xavieraguas/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xavieraguas/Documents/GitHub/Centro Jambatu/amphibians-wiki/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E119E968-4A8C-D14C-8C1E-E945676D3ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D52CB3-A51B-1649-9C43-1B18F54A3D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="40960" windowHeight="20660" xr2:uid="{499C4857-42FD-B04A-B307-0C897FD29869}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Hoja2" sheetId="11" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Appendix II Suppl 1'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Appendix II Suppl 1'!$A$1:$P$691</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
@@ -8420,7 +8420,7 @@
       <name val="Calibri (Cuerpo)"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8443,6 +8443,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -8491,7 +8497,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -8738,6 +8744,10 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -9894,7 +9904,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Xavier Aguas" refreshedDate="45995.716211921295" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="690" xr:uid="{FF14A8D1-0B55-2449-94C7-6D5F1A30A6F4}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Xavier Aguas" refreshedDate="46114.43074502315" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="690" xr:uid="{FF14A8D1-0B55-2449-94C7-6D5F1A30A6F4}">
   <cacheSource type="worksheet">
     <worksheetSource ref="I1:I691" sheet="Appendix II Suppl 1"/>
   </cacheSource>
@@ -12480,10 +12490,10 @@
       <c r="C1" s="12" t="s">
         <v>697</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="106" t="s">
         <v>2621</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="107" t="s">
         <v>2625</v>
       </c>
       <c r="F1" s="13" t="s">
@@ -44502,7 +44512,7 @@
       <c r="G8894" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P1" xr:uid="{0DCD3EB7-4624-0343-B2FC-08EA3165A11C}">
+  <autoFilter ref="A1:P691" xr:uid="{0DCD3EB7-4624-0343-B2FC-08EA3165A11C}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P692">
       <sortCondition ref="C1:C692"/>
     </sortState>
